--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -11,9 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>الاسم الكامل</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+  <si>
+    <t>الاسم بالعربية</t>
+  </si>
+  <si>
+    <t>الاسم بالإنجليزية</t>
   </si>
   <si>
     <t>البريد الإلكتروني</t>
@@ -31,6 +34,9 @@
     <t>الجنس</t>
   </si>
   <si>
+    <t>نوع الإعاقة السمعية</t>
+  </si>
+  <si>
     <t>المؤهل الدراسي</t>
   </si>
   <si>
@@ -83,13 +89,97 @@
   </si>
   <si>
     <t>٦‏/٤‏/٢٠٢٦</t>
+  </si>
+  <si>
+    <t>محمد</t>
+  </si>
+  <si>
+    <t>Mohamed</t>
+  </si>
+  <si>
+    <t>mo1@gmail.com</t>
+  </si>
+  <si>
+    <t>01233654898</t>
+  </si>
+  <si>
+    <t>EVC-1D9353ED</t>
+  </si>
+  <si>
+    <t>الفيوم</t>
+  </si>
+  <si>
+    <t>أصم</t>
+  </si>
+  <si>
+    <t>sdadssd</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>متوسط</t>
+  </si>
+  <si>
+    <t>١٨‏/٤‏/٢٠٢٦</t>
+  </si>
+  <si>
+    <t>سليم</t>
+  </si>
+  <si>
+    <t>Slem</t>
+  </si>
+  <si>
+    <t>s@gmail.com</t>
+  </si>
+  <si>
+    <t>012236547789</t>
+  </si>
+  <si>
+    <t>EVC-2756CB05</t>
+  </si>
+  <si>
+    <t>الجيزة</t>
+  </si>
+  <si>
+    <t>متكلم</t>
+  </si>
+  <si>
+    <t>sasad</t>
+  </si>
+  <si>
+    <t>عبدالله مدحت النجار</t>
+  </si>
+  <si>
+    <t>Abdallah Medhat Elnagar</t>
+  </si>
+  <si>
+    <t>abdallaelngae419@gmail.com</t>
+  </si>
+  <si>
+    <t>01226058993</t>
+  </si>
+  <si>
+    <t>EVC-81690F31</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>FrontEnd</t>
+  </si>
+  <si>
+    <t>مهارة</t>
+  </si>
+  <si>
+    <t>٢٠‏/٤‏/٢٠٢٦</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -105,6 +195,10 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -158,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -167,6 +261,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,23 +608,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="1" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,43 +662,49 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -684,6 +791,202 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
+    <row r="9" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="86">
   <si>
     <t>الاسم بالعربية</t>
   </si>
@@ -173,6 +173,102 @@
   </si>
   <si>
     <t>٢٠‏/٤‏/٢٠٢٦</t>
+  </si>
+  <si>
+    <t>عبدااله النجار</t>
+  </si>
+  <si>
+    <t>Abdallah Elnagar</t>
+  </si>
+  <si>
+    <t>abdo@gmail.com</t>
+  </si>
+  <si>
+    <t>EVC-31E516B9</t>
+  </si>
+  <si>
+    <t>الدقهلية</t>
+  </si>
+  <si>
+    <t>sssss</t>
+  </si>
+  <si>
+    <t>backend</t>
+  </si>
+  <si>
+    <t>٢١‏/٤‏/٢٠٢٦</t>
+  </si>
+  <si>
+    <t>أحمد وائل بقوش</t>
+  </si>
+  <si>
+    <t>Ahmed wael Bakoush</t>
+  </si>
+  <si>
+    <t>ahmedwael@gmail.com</t>
+  </si>
+  <si>
+    <t>0152369887</t>
+  </si>
+  <si>
+    <t>EVC-06172808</t>
+  </si>
+  <si>
+    <t>UI/UX Design</t>
+  </si>
+  <si>
+    <t>abdallaelngae0@gmail.com</t>
+  </si>
+  <si>
+    <t>EVC-B8184811</t>
+  </si>
+  <si>
+    <t>د.رامي يسري</t>
+  </si>
+  <si>
+    <t>Dr/ Ramy Yousry</t>
+  </si>
+  <si>
+    <t>r@gmail.com</t>
+  </si>
+  <si>
+    <t>01223658997</t>
+  </si>
+  <si>
+    <t>EVC-A7908AA3</t>
+  </si>
+  <si>
+    <t>القاهرة</t>
+  </si>
+  <si>
+    <t>مترجم إشارة</t>
+  </si>
+  <si>
+    <t>دكتوراه</t>
+  </si>
+  <si>
+    <t>Signer</t>
+  </si>
+  <si>
+    <t>متقدم</t>
+  </si>
+  <si>
+    <t>تطوير مهني</t>
+  </si>
+  <si>
+    <t>تامر محمد</t>
+  </si>
+  <si>
+    <t>Tamer Mohamed</t>
+  </si>
+  <si>
+    <t>tamer12@gmail.com</t>
+  </si>
+  <si>
+    <t>01156987441</t>
+  </si>
+  <si>
+    <t>EVC-9903CCDC</t>
   </si>
 </sst>
 </file>
@@ -608,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -987,6 +1083,226 @@
         <v>53</v>
       </c>
     </row>
+    <row r="16" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="95">
   <si>
     <t>الاسم بالعربية</t>
   </si>
@@ -269,6 +269,33 @@
   </si>
   <si>
     <t>EVC-9903CCDC</t>
+  </si>
+  <si>
+    <t>سامر</t>
+  </si>
+  <si>
+    <t>Samer</t>
+  </si>
+  <si>
+    <t>samer@gmail.com</t>
+  </si>
+  <si>
+    <t>00000000000</t>
+  </si>
+  <si>
+    <t>EVC-CA088494</t>
+  </si>
+  <si>
+    <t>ماجستير</t>
+  </si>
+  <si>
+    <t>sssssssssssssss</t>
+  </si>
+  <si>
+    <t>sssssssssssss</t>
+  </si>
+  <si>
+    <t>٢٣‏/٤‏/٢٠٢٦</t>
   </si>
 </sst>
 </file>
@@ -704,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -1303,6 +1330,50 @@
         <v>61</v>
       </c>
     </row>
+    <row r="21" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
   <si>
     <t>الاسم بالعربية</t>
   </si>
@@ -296,6 +296,30 @@
   </si>
   <si>
     <t>٢٣‏/٤‏/٢٠٢٦</t>
+  </si>
+  <si>
+    <t>ساهر</t>
+  </si>
+  <si>
+    <t>Saher</t>
+  </si>
+  <si>
+    <t>saher@gmail.com</t>
+  </si>
+  <si>
+    <t>EVC-BB194B20</t>
+  </si>
+  <si>
+    <t>ابتدائي</t>
+  </si>
+  <si>
+    <t>sss</t>
+  </si>
+  <si>
+    <t>ssssss</t>
+  </si>
+  <si>
+    <t>٢٤‏/٤‏/٢٠٢٦</t>
   </si>
 </sst>
 </file>
@@ -731,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -1374,6 +1398,50 @@
         <v>94</v>
       </c>
     </row>
+    <row r="22" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="110">
   <si>
     <t>الاسم بالعربية</t>
   </si>
@@ -320,6 +320,27 @@
   </si>
   <si>
     <t>٢٤‏/٤‏/٢٠٢٦</t>
+  </si>
+  <si>
+    <t>النجار</t>
+  </si>
+  <si>
+    <t>Elnagar</t>
+  </si>
+  <si>
+    <t>elnagar@gmail.com</t>
+  </si>
+  <si>
+    <t>12345678941</t>
+  </si>
+  <si>
+    <t>EVC-B3D8439D</t>
+  </si>
+  <si>
+    <t>3D With Ai</t>
+  </si>
+  <si>
+    <t>٢٨‏/٤‏/٢٠٢٦</t>
   </si>
 </sst>
 </file>
@@ -755,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -1442,6 +1463,50 @@
         <v>102</v>
       </c>
     </row>
+    <row r="23" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
